--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beans" sheetId="1" r:id="Re95b8bb99a30444a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beans" sheetId="1" r:id="R30854e8e25db40f5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -120,7 +120,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="17">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -172,8 +172,38 @@
         <x:fgColor rgb="FFF5F8FB"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="8">
+  <x:borders count="9">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -249,11 +279,25 @@
         <x:color rgb="FFD7E0E8"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="80">
+  <x:cellXfs count="94">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -540,6 +584,53 @@
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="16" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -761,356 +852,986 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="8" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="8" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="8" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="8" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="8" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="13" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="8" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="27" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="8" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="30" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="8" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="28" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="36" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="57" t="str">
+      <x:c r="A1" s="89" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B1" s="57" t="str">
+      <x:c r="B1" s="89" t="str">
         <x:v>full_name</x:v>
       </x:c>
-      <x:c r="C1" s="57" t="str">
+      <x:c r="C1" s="89" t="str">
         <x:v>parent</x:v>
       </x:c>
-      <x:c r="D1" s="57" t="str">
+      <x:c r="D1" s="89" t="str">
         <x:v>valueType</x:v>
       </x:c>
-      <x:c r="E1" s="57" t="str">
+      <x:c r="E1" s="89" t="str">
         <x:v>alias</x:v>
       </x:c>
-      <x:c r="F1" s="57" t="str">
+      <x:c r="F1" s="89" t="str">
         <x:v>sep</x:v>
       </x:c>
-      <x:c r="G1" s="57" t="str">
+      <x:c r="G1" s="89" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="H1" s="57" t="str">
+      <x:c r="H1" s="89" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="I1" s="57" t="str">
+      <x:c r="I1" s="89" t="str">
         <x:v>group</x:v>
       </x:c>
-      <x:c r="J1" s="57" t="str">
+      <x:c r="J1" s="89" t="str">
         <x:v>*fields</x:v>
       </x:c>
-      <x:c r="K1" s="57"/>
-      <x:c r="L1" s="57"/>
-      <x:c r="M1" s="57"/>
-      <x:c r="N1" s="57"/>
-      <x:c r="O1" s="57"/>
-      <x:c r="P1" s="57"/>
+      <x:c r="K1" s="89"/>
+      <x:c r="L1" s="89"/>
+      <x:c r="M1" s="89"/>
+      <x:c r="N1" s="89"/>
+      <x:c r="O1" s="89"/>
+      <x:c r="P1" s="89"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="59" t="str">
+      <x:c r="A2" s="91" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B2" s="59"/>
-      <x:c r="C2" s="59"/>
-      <x:c r="D2" s="59"/>
-      <x:c r="E2" s="59"/>
-      <x:c r="F2" s="59"/>
-      <x:c r="G2" s="59"/>
-      <x:c r="H2" s="59"/>
-      <x:c r="I2" s="59"/>
-      <x:c r="J2" s="59" t="str">
+      <x:c r="B2" s="91"/>
+      <x:c r="C2" s="91"/>
+      <x:c r="D2" s="91"/>
+      <x:c r="E2" s="91"/>
+      <x:c r="F2" s="91"/>
+      <x:c r="G2" s="91"/>
+      <x:c r="H2" s="91"/>
+      <x:c r="I2" s="91"/>
+      <x:c r="J2" s="91" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="K2" s="59" t="str">
+      <x:c r="K2" s="91" t="str">
         <x:v>alias</x:v>
       </x:c>
-      <x:c r="L2" s="59" t="str">
+      <x:c r="L2" s="91" t="str">
         <x:v>type</x:v>
       </x:c>
-      <x:c r="M2" s="59" t="str">
+      <x:c r="M2" s="91" t="str">
         <x:v>group</x:v>
       </x:c>
-      <x:c r="N2" s="59" t="str">
+      <x:c r="N2" s="91" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="O2" s="59" t="str">
+      <x:c r="O2" s="91" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="P2" s="59" t="str">
+      <x:c r="P2" s="91" t="str">
         <x:v>variants</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="62" t="str">
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="93" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3" s="63" t="str">
+      <x:c r="B3" s="93" t="str">
         <x:v>完整类型名</x:v>
       </x:c>
-      <x:c r="C3" s="63" t="str">
+      <x:c r="C3" s="93" t="str">
         <x:v>父类型</x:v>
       </x:c>
-      <x:c r="D3" s="63" t="str">
+      <x:c r="D3" s="93" t="str">
         <x:v>值类型</x:v>
       </x:c>
-      <x:c r="E3" s="63" t="str">
+      <x:c r="E3" s="93" t="str">
         <x:v>别名</x:v>
       </x:c>
-      <x:c r="F3" s="63" t="str">
+      <x:c r="F3" s="93" t="str">
         <x:v>分隔符</x:v>
       </x:c>
-      <x:c r="G3" s="63" t="str">
+      <x:c r="G3" s="93" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="H3" s="63" t="str">
+      <x:c r="H3" s="93" t="str">
         <x:v>标签</x:v>
       </x:c>
-      <x:c r="I3" s="63" t="str">
+      <x:c r="I3" s="93" t="str">
         <x:v>分组</x:v>
       </x:c>
-      <x:c r="J3" s="63" t="str">
+      <x:c r="J3" s="93" t="str">
         <x:v>字段名</x:v>
       </x:c>
-      <x:c r="K3" s="63" t="str">
+      <x:c r="K3" s="93" t="str">
         <x:v>别名</x:v>
       </x:c>
-      <x:c r="L3" s="63" t="str">
+      <x:c r="L3" s="93" t="str">
         <x:v>字段类型</x:v>
       </x:c>
-      <x:c r="M3" s="63" t="str">
+      <x:c r="M3" s="93" t="str">
         <x:v>分组</x:v>
       </x:c>
-      <x:c r="N3" s="63" t="str">
+      <x:c r="N3" s="93" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="O3" s="63" t="str">
+      <x:c r="O3" s="93" t="str">
         <x:v>标签</x:v>
       </x:c>
-      <x:c r="P3" s="63" t="str">
+      <x:c r="P3" s="93" t="str">
         <x:v>变体</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="54" customHeight="1">
-      <x:c r="A4" s="67"/>
-      <x:c r="B4" s="68" t="str">
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="80"/>
+      <x:c r="B4" s="80" t="str">
         <x:v>AttributeValue</x:v>
       </x:c>
-      <x:c r="C4" s="68"/>
-      <x:c r="D4" s="69" t="b">
+      <x:c r="C4" s="80"/>
+      <x:c r="D4" s="81" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E4" s="68"/>
-      <x:c r="F4" s="68" t="str">
+      <x:c r="E4" s="80"/>
+      <x:c r="F4" s="80" t="str">
         <x:v>:</x:v>
       </x:c>
-      <x:c r="G4" s="68" t="str">
+      <x:c r="G4" s="80" t="str">
         <x:v>属性值；由属性方案显式配置</x:v>
       </x:c>
-      <x:c r="H4" s="68"/>
-      <x:c r="I4" s="68" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="J4" s="68" t="str">
+      <x:c r="H4" s="80"/>
+      <x:c r="I4" s="80" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="J4" s="80" t="str">
         <x:v>attributeId</x:v>
       </x:c>
-      <x:c r="K4" s="68"/>
-      <x:c r="L4" s="68" t="str">
+      <x:c r="K4" s="80"/>
+      <x:c r="L4" s="80" t="str">
         <x:v>int#ref=TbAttribute</x:v>
       </x:c>
-      <x:c r="M4" s="68" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="N4" s="68" t="str">
+      <x:c r="M4" s="80" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N4" s="80" t="str">
         <x:v>属性ID</x:v>
       </x:c>
-      <x:c r="O4" s="68"/>
-      <x:c r="P4" s="68"/>
-    </x:row>
-    <x:row r="5" ht="28" customHeight="1">
-      <x:c r="A5" s="78"/>
-      <x:c r="B5" s="78"/>
-      <x:c r="C5" s="78"/>
-      <x:c r="D5" s="78"/>
-      <x:c r="E5" s="78"/>
-      <x:c r="F5" s="78"/>
-      <x:c r="G5" s="78"/>
-      <x:c r="H5" s="78"/>
-      <x:c r="I5" s="78"/>
-      <x:c r="J5" s="78" t="str">
+      <x:c r="O4" s="80"/>
+      <x:c r="P4" s="80"/>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="80"/>
+      <x:c r="B5" s="80"/>
+      <x:c r="C5" s="80"/>
+      <x:c r="D5" s="80"/>
+      <x:c r="E5" s="80"/>
+      <x:c r="F5" s="80"/>
+      <x:c r="G5" s="80"/>
+      <x:c r="H5" s="80"/>
+      <x:c r="I5" s="80"/>
+      <x:c r="J5" s="80" t="str">
         <x:v>valueMilli</x:v>
       </x:c>
-      <x:c r="K5" s="78"/>
-      <x:c r="L5" s="78" t="str">
+      <x:c r="K5" s="80"/>
+      <x:c r="L5" s="80" t="str">
         <x:v>long</x:v>
       </x:c>
-      <x:c r="M5" s="78" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="N5" s="78" t="str">
+      <x:c r="M5" s="80" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N5" s="80" t="str">
         <x:v>属性基础值；原单位×1000；实际值=表值/1000；最多3位小数</x:v>
       </x:c>
-      <x:c r="O5" s="78"/>
-      <x:c r="P5" s="78"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="78"/>
-      <x:c r="B6" s="78" t="str">
+      <x:c r="O5" s="80"/>
+      <x:c r="P5" s="80"/>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="80"/>
+      <x:c r="B6" s="80" t="str">
         <x:v>MonsterWeight</x:v>
       </x:c>
-      <x:c r="C6" s="78"/>
-      <x:c r="D6" s="79" t="b">
+      <x:c r="C6" s="80"/>
+      <x:c r="D6" s="81" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E6" s="78"/>
-      <x:c r="F6" s="78" t="str">
+      <x:c r="E6" s="80"/>
+      <x:c r="F6" s="80" t="str">
         <x:v>:</x:v>
       </x:c>
-      <x:c r="G6" s="78" t="str">
+      <x:c r="G6" s="80" t="str">
         <x:v>刷怪怪物与权重</x:v>
       </x:c>
-      <x:c r="H6" s="78"/>
-      <x:c r="I6" s="78" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="J6" s="78" t="str">
+      <x:c r="H6" s="80"/>
+      <x:c r="I6" s="80" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="J6" s="80" t="str">
         <x:v>monsterId</x:v>
       </x:c>
-      <x:c r="K6" s="78"/>
-      <x:c r="L6" s="78" t="str">
+      <x:c r="K6" s="80"/>
+      <x:c r="L6" s="80" t="str">
         <x:v>int#ref=TbMonster</x:v>
       </x:c>
-      <x:c r="M6" s="78" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="N6" s="78" t="str">
+      <x:c r="M6" s="80" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N6" s="80" t="str">
         <x:v>怪物ID</x:v>
       </x:c>
-      <x:c r="O6" s="78"/>
-      <x:c r="P6" s="78"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="78"/>
-      <x:c r="B7" s="78"/>
-      <x:c r="C7" s="78"/>
-      <x:c r="D7" s="78"/>
-      <x:c r="E7" s="78"/>
-      <x:c r="F7" s="78"/>
-      <x:c r="G7" s="78"/>
-      <x:c r="H7" s="78"/>
-      <x:c r="I7" s="78"/>
-      <x:c r="J7" s="78" t="str">
+      <x:c r="O6" s="80"/>
+      <x:c r="P6" s="80"/>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="80"/>
+      <x:c r="B7" s="80"/>
+      <x:c r="C7" s="80"/>
+      <x:c r="D7" s="80"/>
+      <x:c r="E7" s="80"/>
+      <x:c r="F7" s="80"/>
+      <x:c r="G7" s="80"/>
+      <x:c r="H7" s="80"/>
+      <x:c r="I7" s="80"/>
+      <x:c r="J7" s="80" t="str">
         <x:v>weight</x:v>
       </x:c>
-      <x:c r="K7" s="78"/>
-      <x:c r="L7" s="78" t="str">
+      <x:c r="K7" s="80"/>
+      <x:c r="L7" s="80" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="M7" s="78" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="N7" s="78" t="str">
+      <x:c r="M7" s="80" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N7" s="80" t="str">
         <x:v>正整数权重</x:v>
       </x:c>
-      <x:c r="O7" s="78"/>
-      <x:c r="P7" s="78"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="78"/>
-      <x:c r="B8" s="78" t="str">
+      <x:c r="O7" s="80"/>
+      <x:c r="P7" s="80"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="80"/>
+      <x:c r="B8" s="80" t="str">
         <x:v>RunAttributeModifier</x:v>
       </x:c>
-      <x:c r="C8" s="78"/>
-      <x:c r="D8" s="79" t="b">
+      <x:c r="C8" s="80"/>
+      <x:c r="D8" s="81" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E8" s="78"/>
-      <x:c r="F8" s="78" t="str">
+      <x:c r="E8" s="80"/>
+      <x:c r="F8" s="80" t="str">
         <x:v>:</x:v>
       </x:c>
-      <x:c r="G8" s="78" t="str">
+      <x:c r="G8" s="80" t="str">
         <x:v>局内属性修改项</x:v>
       </x:c>
-      <x:c r="H8" s="78"/>
-      <x:c r="I8" s="78" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="J8" s="78" t="str">
+      <x:c r="H8" s="80"/>
+      <x:c r="I8" s="80" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="J8" s="80" t="str">
         <x:v>attributeId</x:v>
       </x:c>
-      <x:c r="K8" s="78"/>
-      <x:c r="L8" s="78" t="str">
+      <x:c r="K8" s="80"/>
+      <x:c r="L8" s="80" t="str">
         <x:v>int#ref=TbAttribute</x:v>
       </x:c>
-      <x:c r="M8" s="78" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="N8" s="78" t="str">
+      <x:c r="M8" s="80" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N8" s="80" t="str">
         <x:v>属性ID</x:v>
       </x:c>
-      <x:c r="O8" s="78"/>
-      <x:c r="P8" s="78"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="78"/>
-      <x:c r="B9" s="78"/>
-      <x:c r="C9" s="78"/>
-      <x:c r="D9" s="78"/>
-      <x:c r="E9" s="78"/>
-      <x:c r="F9" s="78"/>
-      <x:c r="G9" s="78"/>
-      <x:c r="H9" s="78"/>
-      <x:c r="I9" s="78"/>
-      <x:c r="J9" s="78" t="str">
+      <x:c r="O8" s="80"/>
+      <x:c r="P8" s="80"/>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="80"/>
+      <x:c r="B9" s="80"/>
+      <x:c r="C9" s="80"/>
+      <x:c r="D9" s="80"/>
+      <x:c r="E9" s="80"/>
+      <x:c r="F9" s="80"/>
+      <x:c r="G9" s="80"/>
+      <x:c r="H9" s="80"/>
+      <x:c r="I9" s="80"/>
+      <x:c r="J9" s="80" t="str">
         <x:v>operation</x:v>
       </x:c>
-      <x:c r="K9" s="78"/>
-      <x:c r="L9" s="78" t="str">
+      <x:c r="K9" s="80"/>
+      <x:c r="L9" s="80" t="str">
         <x:v>EAttributeModifyOperation</x:v>
       </x:c>
-      <x:c r="M9" s="78" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="N9" s="78" t="str">
+      <x:c r="M9" s="80" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N9" s="80" t="str">
         <x:v>修改操作</x:v>
       </x:c>
-      <x:c r="O9" s="78"/>
-      <x:c r="P9" s="78"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="78"/>
-      <x:c r="B10" s="78"/>
-      <x:c r="C10" s="78"/>
-      <x:c r="D10" s="78"/>
-      <x:c r="E10" s="78"/>
-      <x:c r="F10" s="78"/>
-      <x:c r="G10" s="78"/>
-      <x:c r="H10" s="78"/>
-      <x:c r="I10" s="78"/>
-      <x:c r="J10" s="78" t="str">
+      <x:c r="O9" s="80"/>
+      <x:c r="P9" s="80"/>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="80"/>
+      <x:c r="B10" s="80"/>
+      <x:c r="C10" s="80"/>
+      <x:c r="D10" s="80"/>
+      <x:c r="E10" s="80"/>
+      <x:c r="F10" s="80"/>
+      <x:c r="G10" s="80"/>
+      <x:c r="H10" s="80"/>
+      <x:c r="I10" s="80"/>
+      <x:c r="J10" s="80" t="str">
         <x:v>valueMilli</x:v>
       </x:c>
-      <x:c r="K10" s="78"/>
-      <x:c r="L10" s="78" t="str">
+      <x:c r="K10" s="80"/>
+      <x:c r="L10" s="80" t="str">
         <x:v>long</x:v>
       </x:c>
-      <x:c r="M10" s="78" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="N10" s="78" t="str">
+      <x:c r="M10" s="80" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N10" s="80" t="str">
         <x:v>Add为原单位乘1000；AddPercent为比例乘1000</x:v>
       </x:c>
-      <x:c r="O10" s="78"/>
-      <x:c r="P10" s="78"/>
+      <x:c r="O10" s="80"/>
+      <x:c r="P10" s="80"/>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="80"/>
+      <x:c r="B11" s="80" t="str">
+        <x:v>UpgradePoolEntry</x:v>
+      </x:c>
+      <x:c r="C11" s="80"/>
+      <x:c r="D11" s="81" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" s="80"/>
+      <x:c r="F11" s="80" t="str">
+        <x:v>:</x:v>
+      </x:c>
+      <x:c r="G11" s="80" t="str">
+        <x:v>升级池中的选项与权重</x:v>
+      </x:c>
+      <x:c r="H11" s="80"/>
+      <x:c r="I11" s="80" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="J11" s="80" t="str">
+        <x:v>optionId</x:v>
+      </x:c>
+      <x:c r="K11" s="80"/>
+      <x:c r="L11" s="80" t="str">
+        <x:v>int#ref=TbUpgradeOption</x:v>
+      </x:c>
+      <x:c r="M11" s="80" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N11" s="80" t="str">
+        <x:v>升级选项ID</x:v>
+      </x:c>
+      <x:c r="O11" s="80"/>
+      <x:c r="P11" s="80"/>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="80"/>
+      <x:c r="B12" s="80"/>
+      <x:c r="C12" s="80"/>
+      <x:c r="D12" s="80"/>
+      <x:c r="E12" s="80"/>
+      <x:c r="F12" s="80"/>
+      <x:c r="G12" s="80"/>
+      <x:c r="H12" s="80"/>
+      <x:c r="I12" s="80"/>
+      <x:c r="J12" s="80" t="str">
+        <x:v>weight</x:v>
+      </x:c>
+      <x:c r="K12" s="80"/>
+      <x:c r="L12" s="80" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M12" s="80" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N12" s="80" t="str">
+        <x:v>池内正整数权重</x:v>
+      </x:c>
+      <x:c r="O12" s="80"/>
+      <x:c r="P12" s="80"/>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
+      <x:c r="M13"/>
+      <x:c r="N13"/>
+      <x:c r="O13"/>
+      <x:c r="P13"/>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
+      <x:c r="M14"/>
+      <x:c r="N14"/>
+      <x:c r="O14"/>
+      <x:c r="P14"/>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
+      <x:c r="M15"/>
+      <x:c r="N15"/>
+      <x:c r="O15"/>
+      <x:c r="P15"/>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+      <x:c r="M16"/>
+      <x:c r="N16"/>
+      <x:c r="O16"/>
+      <x:c r="P16"/>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
+      <x:c r="I17"/>
+      <x:c r="J17"/>
+      <x:c r="K17"/>
+      <x:c r="L17"/>
+      <x:c r="M17"/>
+      <x:c r="N17"/>
+      <x:c r="O17"/>
+      <x:c r="P17"/>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
+      <x:c r="I18"/>
+      <x:c r="J18"/>
+      <x:c r="K18"/>
+      <x:c r="L18"/>
+      <x:c r="M18"/>
+      <x:c r="N18"/>
+      <x:c r="O18"/>
+      <x:c r="P18"/>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
+      <x:c r="I19"/>
+      <x:c r="J19"/>
+      <x:c r="K19"/>
+      <x:c r="L19"/>
+      <x:c r="M19"/>
+      <x:c r="N19"/>
+      <x:c r="O19"/>
+      <x:c r="P19"/>
+    </x:row>
+    <x:row r="20" ht="24" customHeight="1">
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+      <x:c r="I20"/>
+      <x:c r="J20"/>
+      <x:c r="K20"/>
+      <x:c r="L20"/>
+      <x:c r="M20"/>
+      <x:c r="N20"/>
+      <x:c r="O20"/>
+      <x:c r="P20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21"/>
+      <x:c r="B21" t="str">
+        <x:v>RunWeaponRank</x:v>
+      </x:c>
+      <x:c r="C21"/>
+      <x:c r="D21" s="35" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E21"/>
+      <x:c r="F21" t="str">
+        <x:v>:</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>武器星级配置</x:v>
+      </x:c>
+      <x:c r="H21"/>
+      <x:c r="I21" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="J21" t="str">
+        <x:v>star</x:v>
+      </x:c>
+      <x:c r="K21"/>
+      <x:c r="L21" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M21" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N21" t="str">
+        <x:v>星级</x:v>
+      </x:c>
+      <x:c r="O21"/>
+      <x:c r="P21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+      <x:c r="G22"/>
+      <x:c r="H22"/>
+      <x:c r="I22"/>
+      <x:c r="J22" t="str">
+        <x:v>skillId</x:v>
+      </x:c>
+      <x:c r="K22"/>
+      <x:c r="L22" t="str">
+        <x:v>int#ref=TbSkill</x:v>
+      </x:c>
+      <x:c r="M22" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N22" t="str">
+        <x:v>本星级技能</x:v>
+      </x:c>
+      <x:c r="O22"/>
+      <x:c r="P22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
+      <x:c r="G23"/>
+      <x:c r="H23"/>
+      <x:c r="I23"/>
+      <x:c r="J23" t="str">
+        <x:v>damagePermille</x:v>
+      </x:c>
+      <x:c r="K23"/>
+      <x:c r="L23" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M23" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N23" t="str">
+        <x:v>伤害千分比</x:v>
+      </x:c>
+      <x:c r="O23"/>
+      <x:c r="P23"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
+      <x:c r="G24"/>
+      <x:c r="H24"/>
+      <x:c r="I24"/>
+      <x:c r="J24" t="str">
+        <x:v>intervalPermille</x:v>
+      </x:c>
+      <x:c r="K24"/>
+      <x:c r="L24" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M24" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N24" t="str">
+        <x:v>间隔千分比</x:v>
+      </x:c>
+      <x:c r="O24"/>
+      <x:c r="P24"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25"/>
+      <x:c r="B25"/>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
+      <x:c r="G25"/>
+      <x:c r="H25"/>
+      <x:c r="I25"/>
+      <x:c r="J25" t="str">
+        <x:v>rangePermille</x:v>
+      </x:c>
+      <x:c r="K25"/>
+      <x:c r="L25" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M25" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N25" t="str">
+        <x:v>范围千分比</x:v>
+      </x:c>
+      <x:c r="O25"/>
+      <x:c r="P25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26"/>
+      <x:c r="B26" t="str">
+        <x:v>RunPassiveRank</x:v>
+      </x:c>
+      <x:c r="C26"/>
+      <x:c r="D26" s="35" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E26"/>
+      <x:c r="F26" t="str">
+        <x:v>:</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>被动等级总效果</x:v>
+      </x:c>
+      <x:c r="H26"/>
+      <x:c r="I26" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="J26" t="str">
+        <x:v>rank</x:v>
+      </x:c>
+      <x:c r="K26"/>
+      <x:c r="L26" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M26" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N26" t="str">
+        <x:v>等级</x:v>
+      </x:c>
+      <x:c r="O26"/>
+      <x:c r="P26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+      <x:c r="G27"/>
+      <x:c r="H27"/>
+      <x:c r="I27"/>
+      <x:c r="J27" t="str">
+        <x:v>attributeId</x:v>
+      </x:c>
+      <x:c r="K27"/>
+      <x:c r="L27" t="str">
+        <x:v>int#ref=TbAttribute</x:v>
+      </x:c>
+      <x:c r="M27" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N27" t="str">
+        <x:v>属性</x:v>
+      </x:c>
+      <x:c r="O27"/>
+      <x:c r="P27"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28"/>
+      <x:c r="B28"/>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
+      <x:c r="G28"/>
+      <x:c r="H28"/>
+      <x:c r="I28"/>
+      <x:c r="J28" t="str">
+        <x:v>operation</x:v>
+      </x:c>
+      <x:c r="K28"/>
+      <x:c r="L28" t="str">
+        <x:v>EAttributeModifyOperation</x:v>
+      </x:c>
+      <x:c r="M28" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N28" t="str">
+        <x:v>修改区</x:v>
+      </x:c>
+      <x:c r="O28"/>
+      <x:c r="P28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+      <x:c r="H29"/>
+      <x:c r="I29"/>
+      <x:c r="J29" t="str">
+        <x:v>valueMilli</x:v>
+      </x:c>
+      <x:c r="K29"/>
+      <x:c r="L29" t="str">
+        <x:v>long</x:v>
+      </x:c>
+      <x:c r="M29" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N29" t="str">
+        <x:v>本等级总值；替换旧等级</x:v>
+      </x:c>
+      <x:c r="O29"/>
+      <x:c r="P29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="B30" t="str">
+        <x:v>TribulationAltar</x:v>
+      </x:c>
+      <x:c r="D30" s="35" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>:</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>借劫炼器切片</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="J30" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="L30" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M30" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N30" t="str">
+        <x:v>坛序号</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="J31" t="str">
+        <x:v>xPixels</x:v>
+      </x:c>
+      <x:c r="L31" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="M31" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N31" t="str">
+        <x:v>世界横坐标像素</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="J32" t="str">
+        <x:v>yPixels</x:v>
+      </x:c>
+      <x:c r="L32" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="M32" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N32" t="str">
+        <x:v>世界纵坐标像素</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="J33" t="str">
+        <x:v>availableAfterMilli</x:v>
+      </x:c>
+      <x:c r="L33" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M33" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N33" t="str">
+        <x:v>解锁时点毫秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="B34" t="str">
+        <x:v>TribulationBossPhase</x:v>
+      </x:c>
+      <x:c r="D34" s="35" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>:</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>借劫炼器切片</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="J34" t="str">
+        <x:v>healthPermille</x:v>
+      </x:c>
+      <x:c r="L34" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M34" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N34" t="str">
+        <x:v>进入阶段生命比例上界</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="J35" t="str">
+        <x:v>intervalMilli</x:v>
+      </x:c>
+      <x:c r="L35" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M35" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N35" t="str">
+        <x:v>落雷波间隔</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="J36" t="str">
+        <x:v>warningMilli</x:v>
+      </x:c>
+      <x:c r="L36" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M36" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N36" t="str">
+        <x:v>锁点预警时长</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="J37" t="str">
+        <x:v>strikeCount</x:v>
+      </x:c>
+      <x:c r="L37" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M37" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N37" t="str">
+        <x:v>每波雷区数量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="J38" t="str">
+        <x:v>radiusPixels</x:v>
+      </x:c>
+      <x:c r="L38" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="M38" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>雷区命中半径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="J39" t="str">
+        <x:v>clearsDomains</x:v>
+      </x:c>
+      <x:c r="L39" t="str">
+        <x:v>bool</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>命中时是否清除相交阵域</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
